--- a/templates/CAPIT EW1 - template.xlsx
+++ b/templates/CAPIT EW1 - template.xlsx
@@ -3,16 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-135" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$38</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1297,14 +1297,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="19.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col width="19.7109375" customWidth="1" style="6" min="1" max="1"/>
     <col width="18.7109375" customWidth="1" style="6" min="2" max="6"/>
     <col hidden="1" width="13" customWidth="1" style="6" min="7" max="7"/>
-    <col width="19.7109375" customWidth="1" style="6" min="8" max="14"/>
-    <col width="19.7109375" customWidth="1" style="6" min="15" max="16384"/>
+    <col width="19.7109375" customWidth="1" style="6" min="8" max="15"/>
+    <col width="19.7109375" customWidth="1" style="6" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1" customFormat="1" s="2">
@@ -1434,98 +1434,98 @@
     <row r="16" ht="15.95" customFormat="1" customHeight="1" s="48">
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C16" s="49" t="n">
-        <v>0.9452056</v>
+        <v>0.95284046</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>0.0002464833163218216</v>
+        <v>-0.0009122160714502003</v>
       </c>
       <c r="E16" s="34" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4542111901502801</v>
+        <v>-1.681001187709702</v>
       </c>
       <c r="H16" s="50" t="n"/>
     </row>
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="48">
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C17" s="52" t="n">
-        <v>0.94497268</v>
+        <v>0.95371045</v>
       </c>
       <c r="D17" s="45" t="n">
-        <v>0.0006710408091907816</v>
+        <v>-9.174899053043806e-05</v>
       </c>
       <c r="E17" s="45" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="46" t="n">
-        <v>1.236571501594033</v>
+        <v>-0.1690719631892084</v>
       </c>
       <c r="H17" s="53" t="n"/>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="48">
       <c r="B18" s="51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C18" s="52" t="n">
-        <v>0.94433899</v>
+        <v>0.9537979599999999</v>
       </c>
       <c r="D18" s="45" t="n">
-        <v>-0.00186173691210223</v>
+        <v>0.0003249647234719877</v>
       </c>
       <c r="E18" s="45" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="46" t="n">
-        <v>-3.430746353187543</v>
+        <v>0.5988340955797204</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="48">
       <c r="B19" s="51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C19" s="52" t="n">
-        <v>0.94610038</v>
+        <v>0.95348811</v>
       </c>
       <c r="D19" s="45" t="n">
-        <v>0.0009093026203996768</v>
+        <v>0.005115177674059002</v>
       </c>
       <c r="E19" s="45" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="46" t="n">
-        <v>1.67563237780869</v>
+        <v>9.426077893770973</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="48">
       <c r="B20" s="51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C20" s="52" t="n">
-        <v>0.94524087</v>
+        <v>0.94863567</v>
       </c>
       <c r="D20" s="45" t="n">
-        <v>0.0006705748580595472</v>
+        <v>-0.001479546204991244</v>
       </c>
       <c r="E20" s="45" t="n">
-        <v>0.0005513106415402369</v>
+        <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="46" t="n">
-        <v>1.216328522493441</v>
+        <v>-2.726458133880227</v>
       </c>
     </row>
     <row r="21" ht="15.95" customHeight="1">
@@ -1566,18 +1566,18 @@
       <c r="A23" s="8" t="n"/>
       <c r="B23" s="36" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C23" s="36" t="inlineStr"/>
       <c r="D23" s="34" t="n">
-        <v>-0.0026346665253002</v>
+        <v>0.003727401699541222</v>
       </c>
       <c r="E23" s="34" t="n">
-        <v>0.00993531358511679</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>-0.2651820199462008</v>
+        <v>0.9796509638459721</v>
       </c>
       <c r="G23" s="17" t="n"/>
     </row>
@@ -1590,13 +1590,13 @@
       </c>
       <c r="C24" s="44" t="inlineStr"/>
       <c r="D24" s="45" t="n">
-        <v>-0.003525140710388119</v>
+        <v>0.005476840808993355</v>
       </c>
       <c r="E24" s="45" t="n">
-        <v>0.01160659890087934</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F24" s="46" t="n">
-        <v>-0.3037186638818929</v>
+        <v>0.4758158616988107</v>
       </c>
       <c r="G24" s="47" t="n"/>
     </row>
@@ -1609,13 +1609,13 @@
       </c>
       <c r="C25" s="44" t="inlineStr"/>
       <c r="D25" s="45" t="n">
-        <v>-0.1137212318354248</v>
+        <v>-0.07515112697290294</v>
       </c>
       <c r="E25" s="45" t="n">
-        <v>0.03529708637135154</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F25" s="46" t="n">
-        <v>-3.22183056808126</v>
+        <v>-2.135056721816454</v>
       </c>
       <c r="G25" s="47" t="n"/>
     </row>
@@ -1623,18 +1623,18 @@
       <c r="A26" s="8" t="n"/>
       <c r="B26" s="44" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 180 dias</t>
         </is>
       </c>
       <c r="C26" s="44" t="inlineStr"/>
       <c r="D26" s="45" t="n">
-        <v>-0.1167298092400935</v>
+        <v>-0.1974537826116575</v>
       </c>
       <c r="E26" s="45" t="n">
-        <v>0.03187906296972676</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F26" s="46" t="n">
-        <v>-3.661644928238428</v>
+        <v>-2.751002603785741</v>
       </c>
       <c r="G26" s="47" t="n"/>
     </row>
@@ -1642,18 +1642,18 @@
       <c r="A27" s="8" t="n"/>
       <c r="B27" s="44" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C27" s="44" t="inlineStr"/>
       <c r="D27" s="45" t="n">
-        <v>-0.09613052053477056</v>
+        <v>-0.1095952300029146</v>
       </c>
       <c r="E27" s="45" t="n">
-        <v>0.03647477632720864</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F27" s="46" t="n">
-        <v>-2.635534202386904</v>
+        <v>-2.879887618940517</v>
       </c>
       <c r="G27" s="47" t="n"/>
     </row>
@@ -1661,172 +1661,183 @@
       <c r="A28" s="8" t="n"/>
       <c r="B28" s="44" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C28" s="44" t="inlineStr"/>
       <c r="D28" s="45" t="n">
-        <v>-0.2016390324506894</v>
+        <v>-0.09613052053477056</v>
       </c>
       <c r="E28" s="45" t="n">
-        <v>0.06951662098827716</v>
+        <v>0.03647477632720864</v>
       </c>
       <c r="F28" s="46" t="n">
-        <v>-2.900587364346902</v>
+        <v>-2.635534202386904</v>
       </c>
       <c r="G28" s="47" t="n"/>
     </row>
     <row r="29" ht="15.95" customHeight="1">
       <c r="A29" s="8" t="n"/>
-      <c r="B29" s="44" t="n"/>
-      <c r="C29" s="44" t="n"/>
-      <c r="D29" s="45" t="n"/>
-      <c r="E29" s="45" t="n"/>
-      <c r="F29" s="46" t="n"/>
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="inlineStr"/>
+      <c r="D29" s="45" t="n">
+        <v>-0.195190304029377</v>
+      </c>
+      <c r="E29" s="45" t="n">
+        <v>0.07591822223000033</v>
+      </c>
+      <c r="F29" s="46" t="n">
+        <v>-2.571059994503458</v>
+      </c>
       <c r="G29" s="47" t="n"/>
     </row>
-    <row r="30" ht="26.1" customHeight="1">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="37" t="inlineStr">
+    <row r="30"/>
+    <row r="31" ht="26.1" customHeight="1">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C30" s="37" t="n"/>
-      <c r="D30" s="37" t="n"/>
-      <c r="E30" s="37" t="n"/>
-      <c r="F30" s="37" t="n"/>
-      <c r="G30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="15.95" customHeight="1">
-      <c r="A31" s="8" t="n"/>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
-      <c r="E31" s="35" t="n">
-        <v>40870202.00669999</v>
-      </c>
-      <c r="F31" s="35" t="n"/>
+      <c r="C31" s="37" t="n"/>
+      <c r="D31" s="37" t="n"/>
+      <c r="E31" s="37" t="n"/>
+      <c r="F31" s="37" t="n"/>
       <c r="G31" s="4" t="n"/>
     </row>
     <row r="32" ht="15.95" customHeight="1">
       <c r="A32" s="8" t="n"/>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C32" s="20" t="n"/>
       <c r="D32" s="20" t="n"/>
       <c r="E32" s="35" t="n">
-        <v>45738368.14528181</v>
+        <v>41200329.4221</v>
       </c>
       <c r="F32" s="35" t="n"/>
       <c r="G32" s="4" t="n"/>
     </row>
     <row r="33" ht="15.95" customHeight="1">
       <c r="A33" s="8" t="n"/>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="35" t="n">
+        <v>45350936.90721136</v>
+      </c>
+      <c r="F33" s="35" t="n"/>
       <c r="G33" s="4" t="n"/>
     </row>
     <row r="34" ht="15.95" customHeight="1">
-      <c r="B34" s="23" t="inlineStr">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="15.95" customHeight="1">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="n"/>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="25" t="n"/>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="B35" s="24" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="n"/>
+      <c r="E35" s="25" t="n"/>
+      <c r="F35" s="25" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="15.95" customHeight="1">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="D35" s="26" t="n"/>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="26" t="n"/>
-      <c r="G35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="15.95" customHeight="1">
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="28" t="n"/>
-      <c r="D36" s="29" t="n"/>
-      <c r="E36" s="29" t="n"/>
-      <c r="F36" s="29" t="n"/>
+      <c r="D36" s="26" t="n"/>
+      <c r="E36" s="26" t="n"/>
+      <c r="F36" s="26" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
-    <row r="37" ht="63.75" customHeight="1">
-      <c r="B37" s="39" t="inlineStr">
+    <row r="37" ht="15.95" customHeight="1">
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="29" t="n"/>
+      <c r="F37" s="29" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="63.75" customHeight="1">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="C37" s="39" t="n"/>
-      <c r="D37" s="39" t="n"/>
-      <c r="E37" s="39" t="n"/>
-      <c r="F37" s="39" t="n"/>
-      <c r="G37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="40" t="n"/>
-      <c r="C38" s="40" t="n"/>
-      <c r="D38" s="40" t="n"/>
-      <c r="E38" s="40" t="n"/>
-      <c r="F38" s="40" t="n"/>
+      <c r="C38" s="39" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="39" t="n"/>
       <c r="G38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
-      <c r="B39" s="30" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="30" t="n"/>
-      <c r="F39" s="30" t="n"/>
+      <c r="B39" s="40" t="n"/>
+      <c r="C39" s="40" t="n"/>
+      <c r="D39" s="40" t="n"/>
+      <c r="E39" s="40" t="n"/>
+      <c r="F39" s="40" t="n"/>
       <c r="G39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
-      <c r="B40" s="31" t="n"/>
-      <c r="C40" s="32" t="n"/>
-      <c r="D40" s="18" t="n"/>
-      <c r="E40" s="18" t="n"/>
-      <c r="F40" s="18" t="n"/>
+      <c r="B40" s="30" t="n"/>
+      <c r="C40" s="30" t="n"/>
+      <c r="D40" s="30" t="n"/>
+      <c r="E40" s="30" t="n"/>
+      <c r="F40" s="30" t="n"/>
       <c r="G40" s="4" t="n"/>
     </row>
     <row r="41">
+      <c r="A41" s="4" t="n"/>
       <c r="B41" s="31" t="n"/>
       <c r="C41" s="32" t="n"/>
       <c r="D41" s="18" t="n"/>
       <c r="E41" s="18" t="n"/>
       <c r="F41" s="18" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="31" t="n"/>
+      <c r="C42" s="32" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="96"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="94"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="25" min="0" max="16383" man="1"/>
   </rowBreaks>
